--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486806_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486806_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4405</v>
+        <v>3.6896</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6645</v>
+        <v>3.4102</v>
       </c>
       <c r="F2" t="n">
-        <v>0.776</v>
+        <v>0.2794</v>
       </c>
       <c r="G2" t="n">
         <v>2.421</v>
@@ -610,13 +610,13 @@
         <v>0.9654</v>
       </c>
       <c r="S2" t="n">
-        <v>5.9849</v>
+        <v>2.234</v>
       </c>
       <c r="T2" t="n">
-        <v>4.9364</v>
+        <v>1.682</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0486</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3631</v>
+        <v>0.0353</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7013</v>
+        <v>-0.129</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3381</v>
+        <v>0.1643</v>
       </c>
       <c r="G3" t="n">
         <v>0.883</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6123</v>
+        <v>-0.2138</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0486</v>
+        <v>-0.4763</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4363</v>
+        <v>0.2625</v>
       </c>
       <c r="V3" t="n">
         <v>2.4554</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.8587</v>
+        <v>-0.9347</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.4382</v>
+        <v>-1.7625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5795</v>
+        <v>0.8278</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6211</v>
@@ -766,13 +766,13 @@
         <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6897</v>
+        <v>0.2343</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8554</v>
+        <v>-0.1797</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1657</v>
+        <v>0.414</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5133</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2752</v>
+        <v>-1.0505</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1183</v>
+        <v>-0.291</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1569</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>-3.4107</v>
@@ -844,13 +844,13 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9144</v>
+        <v>-0.6897</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0761</v>
+        <v>-0.2487</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8383</v>
+        <v>-0.441</v>
       </c>
       <c r="V5" t="n">
         <v>2.0845</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>A. ROMERO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8711</v>
+        <v>-3.1766</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7446</v>
+        <v>-1.435</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1265</v>
+        <v>-1.7416</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.6973</v>
+        <v>-1.5803</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.903</v>
+        <v>-0.6625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2057</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.5857</v>
+        <v>-1.1727</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.6263</v>
+        <v>0.1655</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>-1.3383</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1117</v>
+        <v>-0.4075</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2766</v>
+        <v>-0.828</v>
       </c>
       <c r="O6" t="n">
-        <v>0.165</v>
+        <v>0.4205</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4746</v>
+        <v>-0.0138</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3866</v>
+        <v>-0.2623</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8613</v>
+        <v>0.2484</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2277</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROMERO GARCIA</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.5325</v>
+        <v>-3.3388</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6418</v>
+        <v>-1.6412</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8906</v>
+        <v>-1.6977</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5803</v>
+        <v>-4.6973</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6625</v>
+        <v>-4.903</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0.2057</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1727</v>
+        <v>-2.5857</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1655</v>
+        <v>-2.6263</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3383</v>
+        <v>0.0407</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4075</v>
+        <v>-2.1117</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.828</v>
+        <v>-2.2766</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4205</v>
+        <v>0.165</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4691</v>
+        <v>-0.2832</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0994</v>
+        <v>0.2901</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.741</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.741</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SECK DIOP</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.6364</v>
+        <v>-4.3545</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0203</v>
+        <v>-2.4706</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6161</v>
+        <v>-1.8839</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8005</v>
+        <v>-5.6762</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6829</v>
+        <v>-4.7854</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1176</v>
+        <v>-0.8908</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9236</v>
+        <v>-2.7438</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2341</v>
+        <v>-2.095</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6895</v>
+        <v>-0.6488</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8769</v>
+        <v>-2.9324</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4488</v>
+        <v>-2.6905</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5719</v>
+        <v>-0.242</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3918</v>
+        <v>-0.8207</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1659</v>
+        <v>-0.5177</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2259</v>
+        <v>-0.303</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>1.7563</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.7563</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1467</v>
+        <v>-4.4543</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.838</v>
+        <v>-4.3691</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3087</v>
+        <v>-0.0852</v>
       </c>
       <c r="G9" t="n">
         <v>-4.7242</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2374</v>
+        <v>0.455</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1107</v>
+        <v>0.3581</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1267</v>
+        <v>0.0968</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5712</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>K. SECK DIOP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2274</v>
+        <v>-4.6101</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1945</v>
+        <v>-4.0685</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0329</v>
+        <v>-0.5416</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.6762</v>
+        <v>-2.8005</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.7854</v>
+        <v>-2.6829</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8908</v>
+        <v>-0.1176</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7438</v>
+        <v>-1.9236</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.095</v>
+        <v>-1.2341</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6488</v>
+        <v>-0.6895</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9324</v>
+        <v>-0.8769</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6905</v>
+        <v>-1.4488</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.242</v>
+        <v>0.5719</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3862</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6937</v>
+        <v>-0.3655</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2417</v>
+        <v>-0.2141</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.452</v>
+        <v>-0.1514</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7563</v>
+        <v>-0.2856</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7563</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.4706</v>
+        <v>-18.1946</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.0325</v>
+        <v>-12.7567</v>
       </c>
       <c r="F11" t="n">
         <v>-5.4381</v>
@@ -1282,7 +1282,7 @@
         <v>-14.8259</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.3805</v>
+        <v>-5.380500000000001</v>
       </c>
       <c r="J11" t="n">
         <v>-10.0247</v>
@@ -1291,7 +1291,7 @@
         <v>-1.0276</v>
       </c>
       <c r="L11" t="n">
-        <v>-8.9971</v>
+        <v>-8.997100000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-10.1817</v>
@@ -1303,7 +1303,7 @@
         <v>3.6166</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0001000000000001</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q11" t="n">
         <v>-11.5848</v>
@@ -1312,13 +1312,13 @@
         <v>11.5846</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5504999999999993</v>
+        <v>0.8267</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4177000000000004</v>
+        <v>-0.1419000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9683999999999999</v>
+        <v>0.9682999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>1.185099999999999</v>
@@ -1327,7 +1327,7 @@
         <v>8.9946</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.8095</v>
+        <v>-7.809499999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.640499999999999</v>
+        <v>9.1617</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2952</v>
+        <v>4.3986</v>
       </c>
       <c r="F12" t="n">
-        <v>5.3453</v>
+        <v>4.7631</v>
       </c>
       <c r="G12" t="n">
         <v>4.6981</v>
@@ -1390,13 +1390,13 @@
         <v>1.7377</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7066</v>
+        <v>0.2278</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2486</v>
+        <v>-0.1452</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9552</v>
+        <v>0.373</v>
       </c>
       <c r="V12" t="n">
         <v>2.498</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5872</v>
+        <v>4.0158</v>
       </c>
       <c r="E13" t="n">
-        <v>4.58</v>
+        <v>3.8926</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0073</v>
+        <v>0.1231</v>
       </c>
       <c r="G13" t="n">
-        <v>4.2417</v>
+        <v>6.112</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7376</v>
+        <v>3.7383</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5041</v>
+        <v>2.3737</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0633</v>
+        <v>5.7614</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9797</v>
+        <v>4.4976</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0837</v>
+        <v>1.2637</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1783</v>
+        <v>0.3506</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7579</v>
+        <v>-0.7593</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4205</v>
+        <v>1.1099</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3862</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3862</v>
+        <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8162</v>
+        <v>-0.1309</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5166</v>
+        <v>-0.2003</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7004</v>
+        <v>0.0694</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8568</v>
+        <v>-0.6138</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8568</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5834</v>
+        <v>3.9503</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6564</v>
+        <v>3.5457</v>
       </c>
       <c r="F14" t="n">
-        <v>2.927</v>
+        <v>0.4046</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7381</v>
+        <v>4.2417</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6688</v>
+        <v>3.7376</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0693</v>
+        <v>0.5041</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2913</v>
+        <v>3.0633</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3251</v>
+        <v>2.9797</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0338</v>
+        <v>0.0837</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4469</v>
+        <v>1.1783</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3437</v>
+        <v>0.7579</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1032</v>
+        <v>0.4205</v>
       </c>
       <c r="P14" t="n">
         <v>0.3862</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7447</v>
+        <v>0.1793</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3305</v>
+        <v>0.4824</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4142</v>
+        <v>-0.3031</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2856</v>
+        <v>-0.8568</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2856</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4353</v>
+        <v>3.5352</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3755</v>
+        <v>0.3461</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0597</v>
+        <v>3.1891</v>
       </c>
       <c r="G15" t="n">
-        <v>6.112</v>
+        <v>2.7381</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7383</v>
+        <v>1.6688</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3737</v>
+        <v>1.0693</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7614</v>
+        <v>1.2913</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4976</v>
+        <v>1.3251</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2637</v>
+        <v>-0.0338</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3506</v>
+        <v>1.4469</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7593</v>
+        <v>0.3437</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1099</v>
+        <v>1.1032</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7114</v>
+        <v>0.6965</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7174</v>
+        <v>0.0202</v>
       </c>
       <c r="U15" t="n">
-        <v>0.006</v>
+        <v>0.6763</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8415</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7861</v>
+        <v>2.6014</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0049</v>
+        <v>-0.6254</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7909</v>
+        <v>3.2268</v>
       </c>
       <c r="G16" t="n">
         <v>0.7984</v>
@@ -1702,13 +1702,13 @@
         <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2813</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7168</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4355</v>
+        <v>0.0004</v>
       </c>
       <c r="V16" t="n">
         <v>1.5133</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TEVAR TEVAR</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2373</v>
+        <v>1.2047</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6415</v>
+        <v>-1.164</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5958</v>
+        <v>2.3687</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6415</v>
+        <v>3.84</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6415</v>
+        <v>3.2274</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.6127</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6415</v>
+        <v>2.2548</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6415</v>
+        <v>2.3316</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.5853</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.8958</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.6895</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3862</v>
+        <v>-2.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2097</v>
+        <v>-0.0827</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.414</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2097</v>
+        <v>0.3313</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>M. TEVAR TEVAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4544</v>
+        <v>1.138</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5777</v>
+        <v>0.6415</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0321</v>
+        <v>0.4965</v>
       </c>
       <c r="G18" t="n">
-        <v>3.84</v>
+        <v>0.6415</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2274</v>
+        <v>0.6415</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6127</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2548</v>
+        <v>0.6415</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3316</v>
+        <v>0.6415</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5853</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8958</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6895</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.51</v>
+        <v>0.3862</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.833</v>
+        <v>0.1104</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8277</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0052</v>
+        <v>0.1104</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1617</v>
+        <v>-0.112</v>
       </c>
       <c r="E19" t="n">
         <v>0.1088</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2705</v>
+        <v>-0.2209</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0764</v>
@@ -1936,13 +1936,13 @@
         <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0276</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V19" t="n">
         <v>0.5712</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5903</v>
+        <v>-0.3189</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.919</v>
+        <v>-0.4018</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3286</v>
+        <v>0.0829</v>
       </c>
       <c r="G20" t="n">
         <v>0.4523</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4022</v>
+        <v>-0.1308</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8829</v>
+        <v>-0.3658</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4807</v>
+        <v>0.235</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7989</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6905</v>
+        <v>-1.2161</v>
       </c>
       <c r="E21" t="n">
         <v>-0.8219</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8686</v>
+        <v>-0.3942</v>
       </c>
       <c r="G21" t="n">
         <v>0.1397</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8881</v>
+        <v>-0.4137</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1934</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6947</v>
+        <v>-0.2203</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9421</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.811</v>
+        <v>-4.1104</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8958</v>
+        <v>-4.4821</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0848</v>
+        <v>0.3717</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3792</v>
@@ -2170,13 +2170,13 @@
         <v>1.1585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3972</v>
+        <v>0.3034</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5518</v>
+        <v>-0.1381</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1546</v>
+        <v>0.4415</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>18.4707</v>
+        <v>19.8497</v>
       </c>
       <c r="E23" t="n">
-        <v>5.438099999999999</v>
+        <v>5.438100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>13.0324</v>
+        <v>14.4114</v>
       </c>
       <c r="G23" t="n">
         <v>20.2062</v>
@@ -2218,7 +2218,7 @@
         <v>14.8259</v>
       </c>
       <c r="I23" t="n">
-        <v>5.3805</v>
+        <v>5.380500000000001</v>
       </c>
       <c r="J23" t="n">
         <v>10.1818</v>
@@ -2239,7 +2239,7 @@
         <v>8.9971</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0002999999999999114</v>
+        <v>0.0003000000000001335</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.5848</v>
@@ -2248,13 +2248,13 @@
         <v>11.5848</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5506999999999997</v>
+        <v>0.8282999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9682999999999999</v>
+        <v>-0.9684</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4177000000000001</v>
+        <v>1.7967</v>
       </c>
       <c r="V23" t="n">
         <v>-1.185</v>
